--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4593,10 +4593,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197446</v>
+        <v>134672964</v>
       </c>
       <c r="B39" t="n">
-        <v>78993</v>
+        <v>79405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4604,40 +4604,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466756</v>
+        <v>466834</v>
       </c>
       <c r="R39" t="n">
-        <v>6858862</v>
+        <v>6858919</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4661,22 +4658,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4685,7 +4672,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4704,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649782</v>
+        <v>129197446</v>
       </c>
       <c r="B40" t="n">
-        <v>79406</v>
+        <v>78993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,21 +4701,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,14 +4724,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466463</v>
+        <v>466756</v>
       </c>
       <c r="R40" t="n">
-        <v>6858687</v>
+        <v>6858862</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,12 +4758,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4793,22 +4789,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129196626</v>
+        <v>129649782</v>
       </c>
       <c r="B41" t="n">
-        <v>81312</v>
+        <v>79406</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4816,21 +4812,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4839,14 +4835,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466807</v>
+        <v>466463</v>
       </c>
       <c r="R41" t="n">
-        <v>6858944</v>
+        <v>6858687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,22 +4869,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4904,22 +4890,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649780</v>
+        <v>129196626</v>
       </c>
       <c r="B42" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4927,21 +4913,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,14 +4936,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466463</v>
+        <v>466807</v>
       </c>
       <c r="R42" t="n">
-        <v>6858687</v>
+        <v>6858944</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,12 +4970,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5005,22 +5001,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129603921</v>
+        <v>129649780</v>
       </c>
       <c r="B43" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5028,34 +5024,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466452</v>
+        <v>466463</v>
       </c>
       <c r="R43" t="n">
-        <v>6858667</v>
+        <v>6858687</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,12 +5081,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5096,25 +5095,26 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129604024</v>
+        <v>129603921</v>
       </c>
       <c r="B44" t="n">
         <v>80433</v>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466487</v>
+        <v>466452</v>
       </c>
       <c r="R44" t="n">
-        <v>6858709</v>
+        <v>6858667</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,7 +5211,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649793</v>
+        <v>129604024</v>
       </c>
       <c r="B45" t="n">
         <v>80433</v>
@@ -5240,16 +5240,13 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466488</v>
+        <v>466487</v>
       </c>
       <c r="R45" t="n">
         <v>6858709</v>
@@ -5279,12 +5276,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,67 +5290,69 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129679929</v>
+        <v>129649793</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sälsjöhållan, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466824</v>
+        <v>466488</v>
       </c>
       <c r="R46" t="n">
-        <v>6858999</v>
+        <v>6858709</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5377,12 +5376,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5391,69 +5390,67 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649815</v>
+        <v>129679929</v>
       </c>
       <c r="B47" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466566</v>
+        <v>466824</v>
       </c>
       <c r="R47" t="n">
-        <v>6858765</v>
+        <v>6858999</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5477,12 +5474,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5491,70 +5488,66 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129196445</v>
+        <v>134673128</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466788</v>
+        <v>466815</v>
       </c>
       <c r="R48" t="n">
-        <v>6858852</v>
+        <v>6858937</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5578,22 +5571,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5602,7 +5585,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5621,51 +5603,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196452</v>
+        <v>134672867</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79397</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466732</v>
+        <v>466800</v>
       </c>
       <c r="R49" t="n">
-        <v>6858915</v>
+        <v>6858920</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5689,22 +5668,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5713,7 +5682,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5732,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129649766</v>
+        <v>129649815</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5743,21 +5711,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5770,10 +5738,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466446</v>
+        <v>466566</v>
       </c>
       <c r="R50" t="n">
-        <v>6858685</v>
+        <v>6858765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5833,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649820</v>
+        <v>134672969</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>83358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5844,40 +5812,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466566</v>
+        <v>466846</v>
       </c>
       <c r="R51" t="n">
-        <v>6858765</v>
+        <v>6858944</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5901,12 +5866,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5915,29 +5880,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196521</v>
+        <v>129196445</v>
       </c>
       <c r="B52" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5945,21 +5909,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5972,10 +5936,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466759</v>
+        <v>466788</v>
       </c>
       <c r="R52" t="n">
-        <v>6858870</v>
+        <v>6858852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6045,10 +6009,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129604003</v>
+        <v>129196452</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6056,37 +6020,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466498</v>
+        <v>466732</v>
       </c>
       <c r="R53" t="n">
-        <v>6858702</v>
+        <v>6858915</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6110,12 +6077,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6124,6 +6101,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6142,10 +6120,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129649789</v>
+        <v>129649766</v>
       </c>
       <c r="B54" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,21 +6131,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6180,10 +6158,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466488</v>
+        <v>466446</v>
       </c>
       <c r="R54" t="n">
-        <v>6858709</v>
+        <v>6858685</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6243,32 +6221,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649784</v>
+        <v>129649820</v>
       </c>
       <c r="B55" t="n">
-        <v>80461</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6281,10 +6259,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466488</v>
+        <v>466566</v>
       </c>
       <c r="R55" t="n">
-        <v>6858709</v>
+        <v>6858765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6344,10 +6322,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649813</v>
+        <v>134672091</v>
       </c>
       <c r="B56" t="n">
-        <v>78334</v>
+        <v>79130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6355,40 +6333,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466566</v>
+        <v>466791</v>
       </c>
       <c r="R56" t="n">
-        <v>6858765</v>
+        <v>6858872</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6412,12 +6387,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6426,29 +6401,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129175069</v>
+        <v>134672160</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>79130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6456,41 +6430,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466837</v>
+        <v>466802</v>
       </c>
       <c r="R57" t="n">
-        <v>6858989</v>
+        <v>6858872</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6514,27 +6484,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6561,46 +6516,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129174937</v>
+        <v>129196521</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6608,10 +6554,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466864</v>
+        <v>466759</v>
       </c>
       <c r="R58" t="n">
-        <v>6858963</v>
+        <v>6858870</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6643,7 +6589,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6653,7 +6599,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6681,60 +6627,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129174947</v>
+        <v>134671962</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466832</v>
+        <v>466786</v>
       </c>
       <c r="R59" t="n">
-        <v>6858949</v>
+        <v>6858834</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6758,22 +6692,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,7 +6706,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6801,60 +6724,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129174959</v>
+        <v>129604003</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466831</v>
+        <v>466498</v>
       </c>
       <c r="R60" t="n">
-        <v>6858936</v>
+        <v>6858702</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6878,22 +6789,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6902,7 +6803,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6921,10 +6821,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196437</v>
+        <v>129649789</v>
       </c>
       <c r="B61" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6932,21 +6832,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6955,14 +6855,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466811</v>
+        <v>466488</v>
       </c>
       <c r="R61" t="n">
-        <v>6858835</v>
+        <v>6858709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6989,22 +6889,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7020,44 +6910,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196477</v>
+        <v>129649784</v>
       </c>
       <c r="B62" t="n">
-        <v>79085</v>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7066,14 +6956,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466786</v>
+        <v>466488</v>
       </c>
       <c r="R62" t="n">
-        <v>6858845</v>
+        <v>6858709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7100,22 +6990,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,22 +7011,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129196486</v>
+        <v>129649813</v>
       </c>
       <c r="B63" t="n">
-        <v>79085</v>
+        <v>78334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7154,21 +7034,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7177,14 +7057,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466760</v>
+        <v>466566</v>
       </c>
       <c r="R63" t="n">
-        <v>6858909</v>
+        <v>6858765</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7211,22 +7091,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7242,22 +7112,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129382885</v>
+        <v>129175069</v>
       </c>
       <c r="B64" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7265,34 +7135,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466572</v>
+        <v>466837</v>
       </c>
       <c r="R64" t="n">
-        <v>6858763</v>
+        <v>6858989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7319,12 +7193,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7351,48 +7240,60 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129603966</v>
+        <v>129174937</v>
       </c>
       <c r="B65" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466467</v>
+        <v>466864</v>
       </c>
       <c r="R65" t="n">
-        <v>6858690</v>
+        <v>6858963</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7416,12 +7317,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7430,6 +7341,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7448,45 +7360,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129604282</v>
+        <v>129174947</v>
       </c>
       <c r="B66" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466572</v>
+        <v>466832</v>
       </c>
       <c r="R66" t="n">
-        <v>6858783</v>
+        <v>6858949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7513,12 +7437,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7527,6 +7461,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7545,45 +7480,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129604483</v>
+        <v>129174959</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466647</v>
+        <v>466831</v>
       </c>
       <c r="R67" t="n">
-        <v>6858779</v>
+        <v>6858936</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7610,12 +7557,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7624,6 +7581,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7642,48 +7600,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649767</v>
+        <v>134671850</v>
       </c>
       <c r="B68" t="n">
-        <v>79085</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466446</v>
+        <v>466808</v>
       </c>
       <c r="R68" t="n">
-        <v>6858685</v>
+        <v>6858812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7710,12 +7665,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7724,26 +7679,25 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129649822</v>
+        <v>129196437</v>
       </c>
       <c r="B69" t="n">
         <v>79085</v>
@@ -7777,14 +7731,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466566</v>
+        <v>466811</v>
       </c>
       <c r="R69" t="n">
-        <v>6858765</v>
+        <v>6858835</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7811,12 +7765,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7832,22 +7796,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197438</v>
+        <v>129196477</v>
       </c>
       <c r="B70" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7855,21 +7819,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7882,10 +7846,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466756</v>
+        <v>466786</v>
       </c>
       <c r="R70" t="n">
-        <v>6858862</v>
+        <v>6858845</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,22 +7876,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7952,6 +7916,1109 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129196486</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>466760</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6858909</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129382885</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>466572</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6858763</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129603966</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>466467</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6858690</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129604282</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>466572</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6858783</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129604483</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>466647</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6858779</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129649767</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>466446</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6858685</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129649822</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134672002</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>466795</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6858864</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134672098</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>466789</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6858878</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134672166</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>466802</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6858872</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129197438</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>466756</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6858862</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196601</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196622</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672964</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649782</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196626</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129603389</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649780</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129603921</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649793</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2463,6 +2548,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138747</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138751</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138755</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2766,6 +2866,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138758</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138762</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138770</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3069,6 +3184,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138773</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138780</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3271,6 +3396,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649656</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3368,6 +3498,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679929</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3465,6 +3600,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673128</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672867</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3663,6 +3808,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649815</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3774,6 +3924,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139291</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3885,6 +4040,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139294</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3996,6 +4156,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139302</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4093,6 +4258,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672969</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4194,6 +4364,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138827</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4295,6 +4470,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138903</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4406,6 +4586,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196445</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4517,6 +4702,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196452</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4618,6 +4808,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649651</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4719,6 +4914,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649766</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4820,6 +5020,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649820</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4917,6 +5122,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129652514</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5014,6 +5224,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672091</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5111,6 +5326,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672160</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5222,6 +5442,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139263</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5333,6 +5558,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196521</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5430,6 +5660,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671962</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5541,6 +5776,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139249</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5638,6 +5878,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604003</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5739,6 +5984,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5840,6 +6090,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649784</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5951,6 +6206,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138933</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6052,6 +6312,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649813</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6168,6 +6433,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139344</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6284,6 +6554,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139355</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6400,6 +6675,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175069</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6516,6 +6796,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281308</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6618,6 +6903,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129603461</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6719,6 +7009,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129758138</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6825,6 +7120,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138713</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6934,6 +7234,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138728</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7054,6 +7359,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174937</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7174,6 +7484,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174947</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7294,6 +7609,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174959</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7391,6 +7711,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671850</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7492,6 +7817,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138892</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7593,6 +7923,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138897</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7694,6 +8029,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138924</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7805,6 +8145,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196437</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7916,6 +8261,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196477</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8027,6 +8377,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196486</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8124,6 +8479,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129382885</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8221,6 +8581,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129603966</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8318,6 +8683,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604282</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8415,6 +8785,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604483</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8516,6 +8891,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649767</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8617,6 +8997,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649822</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8714,6 +9099,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672002</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8811,6 +9201,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672098</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8908,6 +9303,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672166</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9019,8 +9419,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3608,48 +3608,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134672867</v>
+        <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79397</v>
+        <v>79441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466800</v>
+        <v>466823</v>
       </c>
       <c r="R29" t="n">
-        <v>6858920</v>
+        <v>6858936</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3676,9 +3676,19 @@
           <t>2026-06-26</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,68 +3703,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672867</t>
+          <t>https://artportalen.se/Sighting/135833256</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649815</v>
+        <v>134672867</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>79397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466566</v>
+        <v>466800</v>
       </c>
       <c r="R30" t="n">
-        <v>6858765</v>
+        <v>6858920</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3778,12 +3785,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,34 +3799,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649815</t>
+          <t>https://artportalen.se/Sighting/134672867</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139291</v>
+        <v>129649815</v>
       </c>
       <c r="B31" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,21 +3833,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3850,14 +3856,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465965</v>
+        <v>466566</v>
       </c>
       <c r="R31" t="n">
-        <v>6858492</v>
+        <v>6858765</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3884,22 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,24 +3911,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139291</t>
+          <t>https://artportalen.se/Sighting/129649815</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139294</v>
+        <v>129139291</v>
       </c>
       <c r="B32" t="n">
         <v>83307</v>
@@ -3970,10 +3966,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466066</v>
+        <v>465965</v>
       </c>
       <c r="R32" t="n">
-        <v>6858495</v>
+        <v>6858492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,13 +4038,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139294</t>
+          <t>https://artportalen.se/Sighting/129139291</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139302</v>
+        <v>129139294</v>
       </c>
       <c r="B33" t="n">
         <v>83307</v>
@@ -4086,7 +4082,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466064</v>
+        <v>466066</v>
       </c>
       <c r="R33" t="n">
         <v>6858495</v>
@@ -4158,16 +4154,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139302</t>
+          <t>https://artportalen.se/Sighting/129139294</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134672969</v>
+        <v>129139302</v>
       </c>
       <c r="B34" t="n">
-        <v>83358</v>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4193,19 +4189,22 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466846</v>
+        <v>466064</v>
       </c>
       <c r="R34" t="n">
-        <v>6858944</v>
+        <v>6858495</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4229,12 +4228,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,6 +4252,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4260,16 +4270,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672969</t>
+          <t>https://artportalen.se/Sighting/129139302</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129138827</v>
+        <v>134672969</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>83358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,40 +4287,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465992</v>
+        <v>466846</v>
       </c>
       <c r="R35" t="n">
-        <v>6858551</v>
+        <v>6858944</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4334,12 +4341,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4348,7 +4355,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4366,13 +4372,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138827</t>
+          <t>https://artportalen.se/Sighting/134672969</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129138903</v>
+        <v>129138827</v>
       </c>
       <c r="B36" t="n">
         <v>79084</v>
@@ -4410,10 +4416,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465965</v>
+        <v>465992</v>
       </c>
       <c r="R36" t="n">
-        <v>6858521</v>
+        <v>6858551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,13 +4478,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138903</t>
+          <t>https://artportalen.se/Sighting/129138827</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129196445</v>
+        <v>129138903</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4516,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466788</v>
+        <v>465965</v>
       </c>
       <c r="R37" t="n">
-        <v>6858852</v>
+        <v>6858521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4546,22 +4552,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4588,13 +4584,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196445</t>
+          <t>https://artportalen.se/Sighting/129138903</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129196452</v>
+        <v>129196445</v>
       </c>
       <c r="B38" t="n">
         <v>79084</v>
@@ -4632,10 +4628,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466732</v>
+        <v>466788</v>
       </c>
       <c r="R38" t="n">
-        <v>6858915</v>
+        <v>6858852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4704,13 +4700,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196452</t>
+          <t>https://artportalen.se/Sighting/129196445</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649651</v>
+        <v>129196452</v>
       </c>
       <c r="B39" t="n">
         <v>79084</v>
@@ -4744,14 +4740,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465942</v>
+        <v>466732</v>
       </c>
       <c r="R39" t="n">
-        <v>6858506</v>
+        <v>6858915</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4774,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4799,24 +4805,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649651</t>
+          <t>https://artportalen.se/Sighting/129196452</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649766</v>
+        <v>129649651</v>
       </c>
       <c r="B40" t="n">
         <v>79084</v>
@@ -4854,10 +4860,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466446</v>
+        <v>465942</v>
       </c>
       <c r="R40" t="n">
-        <v>6858685</v>
+        <v>6858506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4916,13 +4922,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649766</t>
+          <t>https://artportalen.se/Sighting/129649651</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649820</v>
+        <v>129649766</v>
       </c>
       <c r="B41" t="n">
         <v>79084</v>
@@ -4960,10 +4966,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466566</v>
+        <v>466446</v>
       </c>
       <c r="R41" t="n">
-        <v>6858765</v>
+        <v>6858685</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,13 +5028,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649820</t>
+          <t>https://artportalen.se/Sighting/129649766</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129652514</v>
+        <v>129649820</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -5057,16 +5063,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465718</v>
+        <v>466566</v>
       </c>
       <c r="R42" t="n">
-        <v>6858481</v>
+        <v>6858765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,12 +5102,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,33 +5116,34 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129652514</t>
+          <t>https://artportalen.se/Sighting/129649820</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134672091</v>
+        <v>129652514</v>
       </c>
       <c r="B43" t="n">
-        <v>79130</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5165,13 +5175,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466791</v>
+        <v>465718</v>
       </c>
       <c r="R43" t="n">
-        <v>6858872</v>
+        <v>6858481</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5195,12 +5205,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,13 +5236,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672091</t>
+          <t>https://artportalen.se/Sighting/129652514</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134672160</v>
+        <v>134672091</v>
       </c>
       <c r="B44" t="n">
         <v>79130</v>
@@ -5267,7 +5277,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466802</v>
+        <v>466791</v>
       </c>
       <c r="R44" t="n">
         <v>6858872</v>
@@ -5328,16 +5338,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672160</t>
+          <t>https://artportalen.se/Sighting/134672091</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129139263</v>
+        <v>134672160</v>
       </c>
       <c r="B45" t="n">
-        <v>79946</v>
+        <v>79130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,40 +5355,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465939</v>
+        <v>466802</v>
       </c>
       <c r="R45" t="n">
-        <v>6858553</v>
+        <v>6858872</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5402,22 +5409,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5426,7 +5423,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5444,13 +5440,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139263</t>
+          <t>https://artportalen.se/Sighting/134672160</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129196521</v>
+        <v>129139263</v>
       </c>
       <c r="B46" t="n">
         <v>79946</v>
@@ -5488,10 +5484,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466759</v>
+        <v>465939</v>
       </c>
       <c r="R46" t="n">
-        <v>6858870</v>
+        <v>6858553</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5518,22 +5514,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5560,16 +5556,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196521</t>
+          <t>https://artportalen.se/Sighting/129139263</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134671962</v>
+        <v>129196521</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5595,19 +5591,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466786</v>
+        <v>466759</v>
       </c>
       <c r="R47" t="n">
-        <v>6858834</v>
+        <v>6858870</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5631,12 +5630,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,6 +5654,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5662,16 +5672,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134671962</t>
+          <t>https://artportalen.se/Sighting/129196521</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129139249</v>
+        <v>134671962</v>
       </c>
       <c r="B48" t="n">
-        <v>80432</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5679,40 +5689,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465971</v>
+        <v>466786</v>
       </c>
       <c r="R48" t="n">
-        <v>6858535</v>
+        <v>6858834</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5736,22 +5743,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5760,7 +5757,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5778,13 +5774,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139249</t>
+          <t>https://artportalen.se/Sighting/134671962</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129604003</v>
+        <v>129139249</v>
       </c>
       <c r="B49" t="n">
         <v>80432</v>
@@ -5813,19 +5809,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466498</v>
+        <v>465971</v>
       </c>
       <c r="R49" t="n">
-        <v>6858702</v>
+        <v>6858535</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5849,12 +5848,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5863,6 +5872,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5880,13 +5890,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129604003</t>
+          <t>https://artportalen.se/Sighting/129139249</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129649789</v>
+        <v>129604003</v>
       </c>
       <c r="B50" t="n">
         <v>80432</v>
@@ -5915,22 +5925,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466488</v>
+        <v>466498</v>
       </c>
       <c r="R50" t="n">
-        <v>6858709</v>
+        <v>6858702</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5954,12 +5961,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5968,56 +5975,55 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649789</t>
+          <t>https://artportalen.se/Sighting/129604003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649784</v>
+        <v>129649789</v>
       </c>
       <c r="B51" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6092,38 +6098,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649784</t>
+          <t>https://artportalen.se/Sighting/129649789</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129138933</v>
+        <v>129649784</v>
       </c>
       <c r="B52" t="n">
-        <v>78334</v>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6132,14 +6138,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465973</v>
+        <v>466488</v>
       </c>
       <c r="R52" t="n">
-        <v>6858506</v>
+        <v>6858709</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6166,22 +6172,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6197,24 +6193,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138933</t>
+          <t>https://artportalen.se/Sighting/129649784</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649813</v>
+        <v>129138933</v>
       </c>
       <c r="B53" t="n">
         <v>78334</v>
@@ -6248,14 +6244,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466566</v>
+        <v>465973</v>
       </c>
       <c r="R53" t="n">
-        <v>6858765</v>
+        <v>6858506</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6282,12 +6278,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6303,27 +6309,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649813</t>
+          <t>https://artportalen.se/Sighting/129138933</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129139344</v>
+        <v>129649813</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>78334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6331,38 +6337,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466039</v>
+        <v>466566</v>
       </c>
       <c r="R54" t="n">
-        <v>6858515</v>
+        <v>6858765</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6389,27 +6394,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6418,30 +6408,31 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139344</t>
+          <t>https://artportalen.se/Sighting/129649813</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129139355</v>
+        <v>129139344</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -6480,10 +6471,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466051</v>
+        <v>466039</v>
       </c>
       <c r="R55" t="n">
-        <v>6858500</v>
+        <v>6858515</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6530,7 +6521,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Hackspår.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6556,13 +6547,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129139355</t>
+          <t>https://artportalen.se/Sighting/129139344</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129175069</v>
+        <v>129139355</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -6601,10 +6592,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466837</v>
+        <v>466051</v>
       </c>
       <c r="R56" t="n">
-        <v>6858989</v>
+        <v>6858500</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6631,27 +6622,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Spår av födosök på gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6677,13 +6668,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129175069</t>
+          <t>https://artportalen.se/Sighting/129139355</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129281308</v>
+        <v>129175069</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -6722,10 +6713,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466059</v>
+        <v>466837</v>
       </c>
       <c r="R57" t="n">
-        <v>6858509</v>
+        <v>6858989</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6752,27 +6743,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack gran.</t>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6798,13 +6789,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129281308</t>
+          <t>https://artportalen.se/Sighting/129175069</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129603461</v>
+        <v>129281308</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -6833,21 +6824,20 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466135</v>
+        <v>466059</v>
       </c>
       <c r="R58" t="n">
-        <v>6858496</v>
+        <v>6858509</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6874,12 +6864,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6894,44 +6899,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129603461</t>
+          <t>https://artportalen.se/Sighting/129281308</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129758138</v>
+        <v>129603461</v>
       </c>
       <c r="B59" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6940,23 +6945,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storsvarttjärnen, Hjd</t>
+          <t>Lill-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465990</v>
+        <v>466135</v>
       </c>
       <c r="R59" t="n">
-        <v>6858565</v>
+        <v>6858496</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7011,16 +7017,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129758138</t>
+          <t>https://artportalen.se/Sighting/129603461</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129138713</v>
+        <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>58114</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7028,41 +7034,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465932</v>
+        <v>466134</v>
       </c>
       <c r="R60" t="n">
-        <v>6858501</v>
+        <v>6858488</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7086,17 +7088,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Noterat läten.</t>
+          <t>Färskt på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7111,27 +7123,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138713</t>
+          <t>https://artportalen.se/Sighting/135833257</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129138728</v>
+        <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>58114</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7139,49 +7151,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466017</v>
+        <v>466041</v>
       </c>
       <c r="R61" t="n">
-        <v>6858509</v>
+        <v>6858492</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7205,12 +7205,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>22:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,77 +7240,69 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138728</t>
+          <t>https://artportalen.se/Sighting/135833259</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129174937</v>
+        <v>129758138</v>
       </c>
       <c r="B62" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Storsvarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466864</v>
+        <v>465990</v>
       </c>
       <c r="R62" t="n">
-        <v>6858963</v>
+        <v>6858565</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7319,22 +7326,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7343,70 +7340,61 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129174937</t>
+          <t>https://artportalen.se/Sighting/129758138</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129174947</v>
+        <v>129138713</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7414,10 +7402,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466832</v>
+        <v>465932</v>
       </c>
       <c r="R63" t="n">
-        <v>6858949</v>
+        <v>6858501</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7444,22 +7432,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7468,7 +7451,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7486,52 +7468,52 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129174947</t>
+          <t>https://artportalen.se/Sighting/129138713</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129174959</v>
+        <v>129138728</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7539,10 +7521,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466831</v>
+        <v>466017</v>
       </c>
       <c r="R64" t="n">
-        <v>6858936</v>
+        <v>6858509</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,22 +7551,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7593,7 +7565,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7611,16 +7582,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129174959</t>
+          <t>https://artportalen.se/Sighting/129138728</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134671850</v>
+        <v>129174937</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7645,17 +7616,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466808</v>
+        <v>466864</v>
       </c>
       <c r="R65" t="n">
-        <v>6858812</v>
+        <v>6858963</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7682,12 +7665,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7696,60 +7689,70 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134671850</t>
+          <t>https://artportalen.se/Sighting/129174937</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129138892</v>
+        <v>129174947</v>
       </c>
       <c r="B66" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7757,10 +7760,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465938</v>
+        <v>466832</v>
       </c>
       <c r="R66" t="n">
-        <v>6858496</v>
+        <v>6858949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7787,12 +7790,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7819,43 +7832,52 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138892</t>
+          <t>https://artportalen.se/Sighting/129174947</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129138897</v>
+        <v>129174959</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7863,10 +7885,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465965</v>
+        <v>466831</v>
       </c>
       <c r="R67" t="n">
-        <v>6858521</v>
+        <v>6858936</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7893,12 +7915,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7925,54 +7957,51 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138897</t>
+          <t>https://artportalen.se/Sighting/129174959</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129138924</v>
+        <v>134671850</v>
       </c>
       <c r="B68" t="n">
-        <v>79085</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465973</v>
+        <v>466808</v>
       </c>
       <c r="R68" t="n">
-        <v>6858506</v>
+        <v>6858812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7999,12 +8028,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8013,75 +8042,76 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129138924</t>
+          <t>https://artportalen.se/Sighting/134671850</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196437</v>
+        <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>79085</v>
+        <v>99274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466811</v>
+        <v>466803</v>
       </c>
       <c r="R69" t="n">
-        <v>6858835</v>
+        <v>6858956</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8105,22 +8135,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8129,75 +8164,71 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196437</t>
+          <t>https://artportalen.se/Sighting/135833249</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196477</v>
+        <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>79085</v>
+        <v>99274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466786</v>
+        <v>466809</v>
       </c>
       <c r="R70" t="n">
-        <v>6858845</v>
+        <v>6858955</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8221,22 +8252,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8245,75 +8276,71 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196477</t>
+          <t>https://artportalen.se/Sighting/135833251</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196486</v>
+        <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>99274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466760</v>
+        <v>466804</v>
       </c>
       <c r="R71" t="n">
-        <v>6858909</v>
+        <v>6858964</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8337,22 +8364,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8368,65 +8395,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129196486</t>
+          <t>https://artportalen.se/Sighting/135833252</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129382885</v>
+        <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>79085</v>
+        <v>99274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>A 28359-2026, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466572</v>
+        <v>466837</v>
       </c>
       <c r="R72" t="n">
-        <v>6858763</v>
+        <v>6858945</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8450,12 +8477,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8464,30 +8501,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129382885</t>
+          <t>https://artportalen.se/Sighting/135833255</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129603966</v>
+        <v>129138892</v>
       </c>
       <c r="B73" t="n">
         <v>79085</v>
@@ -8516,19 +8554,22 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466467</v>
+        <v>465938</v>
       </c>
       <c r="R73" t="n">
-        <v>6858690</v>
+        <v>6858496</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8552,12 +8593,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,6 +8607,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8583,13 +8625,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129603966</t>
+          <t>https://artportalen.se/Sighting/129138892</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129604282</v>
+        <v>129138897</v>
       </c>
       <c r="B74" t="n">
         <v>79085</v>
@@ -8618,16 +8660,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466572</v>
+        <v>465965</v>
       </c>
       <c r="R74" t="n">
-        <v>6858783</v>
+        <v>6858521</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8654,12 +8699,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8668,6 +8713,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8685,13 +8731,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129604282</t>
+          <t>https://artportalen.se/Sighting/129138897</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129604483</v>
+        <v>129138924</v>
       </c>
       <c r="B75" t="n">
         <v>79085</v>
@@ -8720,16 +8766,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466647</v>
+        <v>465973</v>
       </c>
       <c r="R75" t="n">
-        <v>6858779</v>
+        <v>6858506</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8756,12 +8805,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,6 +8819,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8787,13 +8837,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129604483</t>
+          <t>https://artportalen.se/Sighting/129138924</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129649767</v>
+        <v>129196437</v>
       </c>
       <c r="B76" t="n">
         <v>79085</v>
@@ -8827,14 +8877,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466446</v>
+        <v>466811</v>
       </c>
       <c r="R76" t="n">
-        <v>6858685</v>
+        <v>6858835</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8861,12 +8911,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8882,24 +8942,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649767</t>
+          <t>https://artportalen.se/Sighting/129196437</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129649822</v>
+        <v>129196477</v>
       </c>
       <c r="B77" t="n">
         <v>79085</v>
@@ -8933,14 +8993,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466566</v>
+        <v>466786</v>
       </c>
       <c r="R77" t="n">
-        <v>6858765</v>
+        <v>6858845</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8967,12 +9027,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8988,27 +9058,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129649822</t>
+          <t>https://artportalen.se/Sighting/129196477</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134672002</v>
+        <v>129196486</v>
       </c>
       <c r="B78" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9034,19 +9104,22 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466795</v>
+        <v>466760</v>
       </c>
       <c r="R78" t="n">
-        <v>6858864</v>
+        <v>6858909</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9070,12 +9143,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9084,6 +9167,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9101,16 +9185,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672002</t>
+          <t>https://artportalen.se/Sighting/129196486</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134672098</v>
+        <v>129382885</v>
       </c>
       <c r="B79" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9142,13 +9226,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466789</v>
+        <v>466572</v>
       </c>
       <c r="R79" t="n">
-        <v>6858878</v>
+        <v>6858763</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9172,12 +9256,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9203,16 +9287,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672098</t>
+          <t>https://artportalen.se/Sighting/129382885</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134672166</v>
+        <v>129603966</v>
       </c>
       <c r="B80" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9244,10 +9328,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466802</v>
+        <v>466467</v>
       </c>
       <c r="R80" t="n">
-        <v>6858872</v>
+        <v>6858690</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9274,12 +9358,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9305,16 +9389,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134672166</t>
+          <t>https://artportalen.se/Sighting/129603966</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129197438</v>
+        <v>129604282</v>
       </c>
       <c r="B81" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9322,37 +9406,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466756</v>
+        <v>466572</v>
       </c>
       <c r="R81" t="n">
-        <v>6858862</v>
+        <v>6858783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9379,22 +9460,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9403,7 +9474,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9420,6 +9490,742 @@
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604282</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129604483</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>466647</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6858779</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129604483</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129649767</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>466446</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6858685</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649767</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129649822</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649822</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134672002</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>466795</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6858864</v>
+      </c>
+      <c r="S85" t="n">
+        <v>20</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672002</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134672098</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>466789</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6858878</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672098</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134672166</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>466802</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6858872</v>
+      </c>
+      <c r="S87" t="n">
+        <v>20</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672166</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129197438</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>466756</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6858862</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129197438</t>
         </is>
@@ -9507,6 +10313,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28359-2026 artfynd.xlsx
+++ b/artfynd/A 28359-2026 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>135833256</v>
       </c>
       <c r="B29" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135833257</v>
       </c>
       <c r="B60" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135833259</v>
       </c>
       <c r="B61" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>135833249</v>
       </c>
       <c r="B69" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>135833251</v>
       </c>
       <c r="B70" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>135833252</v>
       </c>
       <c r="B71" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>135833255</v>
       </c>
       <c r="B72" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
